--- a/diseases/d234/2000-2004.xlsx
+++ b/diseases/d234/2000-2004.xlsx
@@ -927,9 +927,6 @@
       <c r="O3" t="n">
         <v>1</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
         <v>0.01931918608655401</v>
       </c>
@@ -1485,9 +1482,6 @@
       <c r="O6" t="n">
         <v>0</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0</v>
       </c>
@@ -2043,9 +2037,6 @@
       <c r="O9" t="n">
         <v>1</v>
       </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
       <c r="R9" t="n">
         <v>0.01931918608655401</v>
       </c>
@@ -2601,9 +2592,6 @@
       <c r="O12" t="n">
         <v>1</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="R12" t="n">
         <v>0.02226741517840542</v>
       </c>
@@ -3159,9 +3147,6 @@
       <c r="O15" t="n">
         <v>0</v>
       </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
       <c r="R15" t="n">
         <v>0</v>
       </c>
@@ -3717,9 +3702,6 @@
       <c r="O18" t="n">
         <v>0</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="R18" t="n">
         <v>0</v>
       </c>
@@ -4275,9 +4257,6 @@
       <c r="O21" t="n">
         <v>1</v>
       </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
       <c r="R21" t="n">
         <v>0.01931918608655401</v>
       </c>
@@ -4833,9 +4812,6 @@
       <c r="O24" t="n">
         <v>1</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="R24" t="n">
         <v>0.02226741517840542</v>
       </c>
@@ -5391,9 +5367,6 @@
       <c r="O27" t="n">
         <v>0</v>
       </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
       <c r="R27" t="n">
         <v>0</v>
       </c>
@@ -5949,9 +5922,6 @@
       <c r="O30" t="n">
         <v>1</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
         <v>0.02226741517840542</v>
       </c>
@@ -6507,9 +6477,6 @@
       <c r="O33" t="n">
         <v>0</v>
       </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
       <c r="R33" t="n">
         <v>0</v>
       </c>
@@ -7065,9 +7032,6 @@
       <c r="O36" t="n">
         <v>0</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="R36" t="n">
         <v>0</v>
       </c>
@@ -7623,9 +7587,6 @@
       <c r="O39" t="n">
         <v>0</v>
       </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
       <c r="R39" t="n">
         <v>0</v>
       </c>
@@ -8181,9 +8142,6 @@
       <c r="O42" t="n">
         <v>1</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="R42" t="n">
         <v>0.02226741517840542</v>
       </c>
@@ -8739,9 +8697,6 @@
       <c r="O45" t="n">
         <v>0</v>
       </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
       <c r="R45" t="n">
         <v>0</v>
       </c>
@@ -9297,9 +9252,6 @@
       <c r="O48" t="n">
         <v>3</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="R48" t="n">
         <v>0.06680224553521626</v>
       </c>
@@ -9855,9 +9807,6 @@
       <c r="O51" t="n">
         <v>0</v>
       </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
       <c r="R51" t="n">
         <v>0</v>
       </c>
@@ -10413,9 +10362,6 @@
       <c r="O54" t="n">
         <v>5</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="R54" t="n">
         <v>0.1113370758920271</v>
       </c>
@@ -10971,9 +10917,6 @@
       <c r="O57" t="n">
         <v>0</v>
       </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
       <c r="R57" t="n">
         <v>0</v>
       </c>
@@ -11529,9 +11472,6 @@
       <c r="O60" t="n">
         <v>2</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="R60" t="n">
         <v>0.04453483035681084</v>
       </c>
@@ -12087,9 +12027,6 @@
       <c r="O63" t="n">
         <v>0</v>
       </c>
-      <c r="Q63" t="n">
-        <v>0</v>
-      </c>
       <c r="R63" t="n">
         <v>0</v>
       </c>
@@ -12645,9 +12582,6 @@
       <c r="O66" t="n">
         <v>0</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="R66" t="n">
         <v>0</v>
       </c>
@@ -13203,9 +13137,6 @@
       <c r="O69" t="n">
         <v>0</v>
       </c>
-      <c r="Q69" t="n">
-        <v>0</v>
-      </c>
       <c r="R69" t="n">
         <v>0</v>
       </c>
@@ -13761,9 +13692,6 @@
       <c r="O72" t="n">
         <v>1</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
         <v>0.02226741517840542</v>
       </c>
@@ -14319,9 +14247,6 @@
       <c r="O75" t="n">
         <v>0</v>
       </c>
-      <c r="Q75" t="n">
-        <v>0</v>
-      </c>
       <c r="R75" t="n">
         <v>0</v>
       </c>
@@ -14877,9 +14802,6 @@
       <c r="O78" t="n">
         <v>0</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="R78" t="n">
         <v>0</v>
       </c>
@@ -15126,7 +15048,7 @@
       </c>
       <c r="AM79" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN79" t="b">
@@ -15273,9 +15195,6 @@
       <c r="O80" t="n">
         <v>0</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="R80" t="n">
         <v>0</v>
       </c>
@@ -15831,9 +15750,6 @@
       <c r="O83" t="n">
         <v>0</v>
       </c>
-      <c r="Q83" t="n">
-        <v>0</v>
-      </c>
       <c r="R83" t="n">
         <v>0</v>
       </c>
@@ -16389,9 +16305,6 @@
       <c r="O86" t="n">
         <v>3</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="R86" t="n">
         <v>0.006377080873374387</v>
       </c>
@@ -16638,7 +16551,7 @@
       </c>
       <c r="AM87" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN87" t="b">
@@ -16785,9 +16698,6 @@
       <c r="O88" t="n">
         <v>1</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="R88" t="n">
         <v>0.02215498430651687</v>
       </c>
@@ -17343,9 +17253,6 @@
       <c r="O91" t="n">
         <v>0</v>
       </c>
-      <c r="Q91" t="n">
-        <v>0</v>
-      </c>
       <c r="R91" t="n">
         <v>0</v>
       </c>
@@ -17901,9 +17808,6 @@
       <c r="O94" t="n">
         <v>2</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="R94" t="n">
         <v>0.004251387248916258</v>
       </c>
@@ -18150,7 +18054,7 @@
       </c>
       <c r="AM95" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN95" t="b">
@@ -18297,9 +18201,6 @@
       <c r="O96" t="n">
         <v>0</v>
       </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
       <c r="R96" t="n">
         <v>0</v>
       </c>
@@ -18855,9 +18756,6 @@
       <c r="O99" t="n">
         <v>1</v>
       </c>
-      <c r="Q99" t="n">
-        <v>0</v>
-      </c>
       <c r="R99" t="n">
         <v>0.01927535832409241</v>
       </c>
@@ -19413,9 +19311,6 @@
       <c r="O102" t="n">
         <v>2</v>
       </c>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
       <c r="R102" t="n">
         <v>0.004251387248916258</v>
       </c>
@@ -19662,7 +19557,7 @@
       </c>
       <c r="AM103" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN103" t="b">
@@ -19809,9 +19704,6 @@
       <c r="O104" t="n">
         <v>3</v>
       </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
       <c r="R104" t="n">
         <v>0.0664649529195506</v>
       </c>
@@ -20367,9 +20259,6 @@
       <c r="O107" t="n">
         <v>0</v>
       </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
       <c r="R107" t="n">
         <v>0</v>
       </c>
@@ -20925,9 +20814,6 @@
       <c r="O110" t="n">
         <v>5</v>
       </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
       <c r="R110" t="n">
         <v>0.01062846812229064</v>
       </c>
@@ -21174,7 +21060,7 @@
       </c>
       <c r="AM111" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN111" t="b">
@@ -21321,9 +21207,6 @@
       <c r="O112" t="n">
         <v>2</v>
       </c>
-      <c r="Q112" t="n">
-        <v>0</v>
-      </c>
       <c r="R112" t="n">
         <v>0.04430996861303373</v>
       </c>
@@ -21879,9 +21762,6 @@
       <c r="O115" t="n">
         <v>0</v>
       </c>
-      <c r="Q115" t="n">
-        <v>0</v>
-      </c>
       <c r="R115" t="n">
         <v>0</v>
       </c>
@@ -22437,9 +22317,6 @@
       <c r="O118" t="n">
         <v>3</v>
       </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
       <c r="R118" t="n">
         <v>0.006377080873374387</v>
       </c>
@@ -22686,7 +22563,7 @@
       </c>
       <c r="AM119" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN119" t="b">
@@ -22833,9 +22710,6 @@
       <c r="O120" t="n">
         <v>0</v>
       </c>
-      <c r="Q120" t="n">
-        <v>0</v>
-      </c>
       <c r="R120" t="n">
         <v>0</v>
       </c>
@@ -23391,9 +23265,6 @@
       <c r="O123" t="n">
         <v>1</v>
       </c>
-      <c r="Q123" t="n">
-        <v>0</v>
-      </c>
       <c r="R123" t="n">
         <v>0.01927535832409241</v>
       </c>
@@ -23949,9 +23820,6 @@
       <c r="O126" t="n">
         <v>6</v>
       </c>
-      <c r="Q126" t="n">
-        <v>0</v>
-      </c>
       <c r="R126" t="n">
         <v>0.01275416174674877</v>
       </c>
@@ -24198,7 +24066,7 @@
       </c>
       <c r="AM127" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN127" t="b">
@@ -24345,9 +24213,6 @@
       <c r="O128" t="n">
         <v>0</v>
       </c>
-      <c r="Q128" t="n">
-        <v>0</v>
-      </c>
       <c r="R128" t="n">
         <v>0</v>
       </c>
@@ -24903,9 +24768,6 @@
       <c r="O131" t="n">
         <v>1</v>
       </c>
-      <c r="Q131" t="n">
-        <v>0</v>
-      </c>
       <c r="R131" t="n">
         <v>0.01927535832409241</v>
       </c>
@@ -25461,9 +25323,6 @@
       <c r="O134" t="n">
         <v>5</v>
       </c>
-      <c r="Q134" t="n">
-        <v>0</v>
-      </c>
       <c r="R134" t="n">
         <v>0.01062846812229064</v>
       </c>
@@ -25710,7 +25569,7 @@
       </c>
       <c r="AM135" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN135" t="b">
@@ -25857,9 +25716,6 @@
       <c r="O136" t="n">
         <v>3</v>
       </c>
-      <c r="Q136" t="n">
-        <v>0</v>
-      </c>
       <c r="R136" t="n">
         <v>0.0664649529195506</v>
       </c>
@@ -26415,9 +26271,6 @@
       <c r="O139" t="n">
         <v>0</v>
       </c>
-      <c r="Q139" t="n">
-        <v>0</v>
-      </c>
       <c r="R139" t="n">
         <v>0</v>
       </c>
@@ -26973,9 +26826,6 @@
       <c r="O142" t="n">
         <v>5</v>
       </c>
-      <c r="Q142" t="n">
-        <v>0</v>
-      </c>
       <c r="R142" t="n">
         <v>0.01062846812229064</v>
       </c>
@@ -27222,7 +27072,7 @@
       </c>
       <c r="AM143" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN143" t="b">
@@ -27369,9 +27219,6 @@
       <c r="O144" t="n">
         <v>5</v>
       </c>
-      <c r="Q144" t="n">
-        <v>0</v>
-      </c>
       <c r="R144" t="n">
         <v>0.1107749215325843</v>
       </c>
@@ -27927,9 +27774,6 @@
       <c r="O147" t="n">
         <v>3</v>
       </c>
-      <c r="Q147" t="n">
-        <v>0</v>
-      </c>
       <c r="R147" t="n">
         <v>0.05782607497227721</v>
       </c>
@@ -28485,9 +28329,6 @@
       <c r="O150" t="n">
         <v>1</v>
       </c>
-      <c r="Q150" t="n">
-        <v>0</v>
-      </c>
       <c r="R150" t="n">
         <v>0.002125693624458129</v>
       </c>
@@ -28734,7 +28575,7 @@
       </c>
       <c r="AM151" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN151" t="b">
@@ -28881,9 +28722,6 @@
       <c r="O152" t="n">
         <v>2</v>
       </c>
-      <c r="Q152" t="n">
-        <v>0</v>
-      </c>
       <c r="R152" t="n">
         <v>0.04430996861303373</v>
       </c>
@@ -29439,9 +29277,6 @@
       <c r="O155" t="n">
         <v>1</v>
       </c>
-      <c r="Q155" t="n">
-        <v>0</v>
-      </c>
       <c r="R155" t="n">
         <v>0.01927535832409241</v>
       </c>
@@ -29997,9 +29832,6 @@
       <c r="O158" t="n">
         <v>2</v>
       </c>
-      <c r="Q158" t="n">
-        <v>0</v>
-      </c>
       <c r="R158" t="n">
         <v>0.004251387248916258</v>
       </c>
@@ -30246,7 +30078,7 @@
       </c>
       <c r="AM159" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN159" t="b">
@@ -30393,9 +30225,6 @@
       <c r="O160" t="n">
         <v>1</v>
       </c>
-      <c r="Q160" t="n">
-        <v>0</v>
-      </c>
       <c r="R160" t="n">
         <v>0.02215498430651687</v>
       </c>
@@ -30951,9 +30780,6 @@
       <c r="O163" t="n">
         <v>0</v>
       </c>
-      <c r="Q163" t="n">
-        <v>0</v>
-      </c>
       <c r="R163" t="n">
         <v>0</v>
       </c>
@@ -31509,9 +31335,6 @@
       <c r="O166" t="n">
         <v>2</v>
       </c>
-      <c r="Q166" t="n">
-        <v>0</v>
-      </c>
       <c r="R166" t="n">
         <v>0.004251387248916258</v>
       </c>
@@ -31758,7 +31581,7 @@
       </c>
       <c r="AM167" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN167" t="b">
@@ -31905,9 +31728,6 @@
       <c r="O168" t="n">
         <v>2</v>
       </c>
-      <c r="Q168" t="n">
-        <v>0</v>
-      </c>
       <c r="R168" t="n">
         <v>0.04430996861303373</v>
       </c>
@@ -32463,9 +32283,6 @@
       <c r="O171" t="n">
         <v>0</v>
       </c>
-      <c r="Q171" t="n">
-        <v>0</v>
-      </c>
       <c r="R171" t="n">
         <v>0</v>
       </c>
@@ -33021,9 +32838,6 @@
       <c r="O174" t="n">
         <v>3</v>
       </c>
-      <c r="Q174" t="n">
-        <v>0</v>
-      </c>
       <c r="R174" t="n">
         <v>0.006342612649636899</v>
       </c>
@@ -33270,7 +33084,7 @@
       </c>
       <c r="AM175" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN175" t="b">
@@ -33417,9 +33231,6 @@
       <c r="O176" t="n">
         <v>1</v>
       </c>
-      <c r="Q176" t="n">
-        <v>0</v>
-      </c>
       <c r="R176" t="n">
         <v>0.02203607128580917</v>
       </c>
@@ -33975,9 +33786,6 @@
       <c r="O179" t="n">
         <v>0</v>
       </c>
-      <c r="Q179" t="n">
-        <v>0</v>
-      </c>
       <c r="R179" t="n">
         <v>0</v>
       </c>
@@ -34533,9 +34341,6 @@
       <c r="O182" t="n">
         <v>19</v>
       </c>
-      <c r="Q182" t="n">
-        <v>0</v>
-      </c>
       <c r="R182" t="n">
         <v>0.04016988011436703</v>
       </c>
@@ -34782,7 +34587,7 @@
       </c>
       <c r="AM183" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN183" t="b">
@@ -34929,9 +34734,6 @@
       <c r="O184" t="n">
         <v>1</v>
       </c>
-      <c r="Q184" t="n">
-        <v>0</v>
-      </c>
       <c r="R184" t="n">
         <v>0.02203607128580917</v>
       </c>
@@ -35487,9 +35289,6 @@
       <c r="O187" t="n">
         <v>0</v>
       </c>
-      <c r="Q187" t="n">
-        <v>0</v>
-      </c>
       <c r="R187" t="n">
         <v>0</v>
       </c>
@@ -36045,9 +35844,6 @@
       <c r="O190" t="n">
         <v>279</v>
       </c>
-      <c r="Q190" t="n">
-        <v>0</v>
-      </c>
       <c r="R190" t="n">
         <v>0.5898629764162316</v>
       </c>
@@ -36294,7 +36090,7 @@
       </c>
       <c r="AM191" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN191" t="b">
@@ -36441,9 +36237,6 @@
       <c r="O192" t="n">
         <v>1</v>
       </c>
-      <c r="Q192" t="n">
-        <v>0</v>
-      </c>
       <c r="R192" t="n">
         <v>0.02203607128580917</v>
       </c>
@@ -36999,9 +36792,6 @@
       <c r="O195" t="n">
         <v>0</v>
       </c>
-      <c r="Q195" t="n">
-        <v>0</v>
-      </c>
       <c r="R195" t="n">
         <v>0</v>
       </c>
@@ -37557,9 +37347,6 @@
       <c r="O198" t="n">
         <v>69</v>
       </c>
-      <c r="Q198" t="n">
-        <v>0</v>
-      </c>
       <c r="R198" t="n">
         <v>0.1458800909416487</v>
       </c>
@@ -37806,7 +37593,7 @@
       </c>
       <c r="AM199" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN199" t="b">
@@ -37953,9 +37740,6 @@
       <c r="O200" t="n">
         <v>1</v>
       </c>
-      <c r="Q200" t="n">
-        <v>0</v>
-      </c>
       <c r="R200" t="n">
         <v>0.02203607128580917</v>
       </c>
@@ -38511,9 +38295,6 @@
       <c r="O203" t="n">
         <v>0</v>
       </c>
-      <c r="Q203" t="n">
-        <v>0</v>
-      </c>
       <c r="R203" t="n">
         <v>0</v>
       </c>
@@ -39069,9 +38850,6 @@
       <c r="O206" t="n">
         <v>13</v>
       </c>
-      <c r="Q206" t="n">
-        <v>0</v>
-      </c>
       <c r="R206" t="n">
         <v>0.02748465481509323</v>
       </c>
@@ -39318,7 +39096,7 @@
       </c>
       <c r="AM207" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN207" t="b">
@@ -39465,9 +39243,6 @@
       <c r="O208" t="n">
         <v>0</v>
       </c>
-      <c r="Q208" t="n">
-        <v>0</v>
-      </c>
       <c r="R208" t="n">
         <v>0</v>
       </c>
@@ -40023,9 +39798,6 @@
       <c r="O211" t="n">
         <v>1</v>
       </c>
-      <c r="Q211" t="n">
-        <v>0</v>
-      </c>
       <c r="R211" t="n">
         <v>0.01922875021199697</v>
       </c>
@@ -40581,9 +40353,6 @@
       <c r="O214" t="n">
         <v>6</v>
       </c>
-      <c r="Q214" t="n">
-        <v>0</v>
-      </c>
       <c r="R214" t="n">
         <v>0.0126852252992738</v>
       </c>
@@ -40830,7 +40599,7 @@
       </c>
       <c r="AM215" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN215" t="b">
@@ -40977,9 +40746,6 @@
       <c r="O216" t="n">
         <v>1</v>
       </c>
-      <c r="Q216" t="n">
-        <v>0</v>
-      </c>
       <c r="R216" t="n">
         <v>0.02203607128580917</v>
       </c>
@@ -41535,9 +41301,6 @@
       <c r="O219" t="n">
         <v>0</v>
       </c>
-      <c r="Q219" t="n">
-        <v>0</v>
-      </c>
       <c r="R219" t="n">
         <v>0</v>
       </c>
@@ -42093,9 +41856,6 @@
       <c r="O222" t="n">
         <v>7</v>
       </c>
-      <c r="Q222" t="n">
-        <v>0</v>
-      </c>
       <c r="R222" t="n">
         <v>0.01479942951581943</v>
       </c>
@@ -42342,7 +42102,7 @@
       </c>
       <c r="AM223" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN223" t="b">
@@ -42489,9 +42249,6 @@
       <c r="O224" t="n">
         <v>1</v>
       </c>
-      <c r="Q224" t="n">
-        <v>0</v>
-      </c>
       <c r="R224" t="n">
         <v>0.02203607128580917</v>
       </c>
@@ -43047,9 +42804,6 @@
       <c r="O227" t="n">
         <v>0</v>
       </c>
-      <c r="Q227" t="n">
-        <v>0</v>
-      </c>
       <c r="R227" t="n">
         <v>0</v>
       </c>
@@ -43605,9 +43359,6 @@
       <c r="O230" t="n">
         <v>5</v>
       </c>
-      <c r="Q230" t="n">
-        <v>0</v>
-      </c>
       <c r="R230" t="n">
         <v>0.01057102108272817</v>
       </c>
@@ -43854,7 +43605,7 @@
       </c>
       <c r="AM231" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN231" t="b">
@@ -44001,9 +43752,6 @@
       <c r="O232" t="n">
         <v>1</v>
       </c>
-      <c r="Q232" t="n">
-        <v>0</v>
-      </c>
       <c r="R232" t="n">
         <v>0.02203607128580917</v>
       </c>
@@ -44559,9 +44307,6 @@
       <c r="O235" t="n">
         <v>0</v>
       </c>
-      <c r="Q235" t="n">
-        <v>0</v>
-      </c>
       <c r="R235" t="n">
         <v>0</v>
       </c>
@@ -45117,9 +44862,6 @@
       <c r="O238" t="n">
         <v>3</v>
       </c>
-      <c r="Q238" t="n">
-        <v>0</v>
-      </c>
       <c r="R238" t="n">
         <v>0.006342612649636899</v>
       </c>
@@ -45366,7 +45108,7 @@
       </c>
       <c r="AM239" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN239" t="b">
@@ -45513,9 +45255,6 @@
       <c r="O240" t="n">
         <v>1</v>
       </c>
-      <c r="Q240" t="n">
-        <v>0</v>
-      </c>
       <c r="R240" t="n">
         <v>0.02203607128580917</v>
       </c>
@@ -46071,9 +45810,6 @@
       <c r="O243" t="n">
         <v>0</v>
       </c>
-      <c r="Q243" t="n">
-        <v>0</v>
-      </c>
       <c r="R243" t="n">
         <v>0</v>
       </c>
@@ -46629,9 +46365,6 @@
       <c r="O246" t="n">
         <v>1</v>
       </c>
-      <c r="Q246" t="n">
-        <v>0</v>
-      </c>
       <c r="R246" t="n">
         <v>0.002114204216545633</v>
       </c>
@@ -46878,7 +46611,7 @@
       </c>
       <c r="AM247" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN247" t="b">
@@ -47025,9 +46758,6 @@
       <c r="O248" t="n">
         <v>3</v>
       </c>
-      <c r="Q248" t="n">
-        <v>0</v>
-      </c>
       <c r="R248" t="n">
         <v>0.0661082138574275</v>
       </c>
@@ -47583,9 +47313,6 @@
       <c r="O251" t="n">
         <v>0</v>
       </c>
-      <c r="Q251" t="n">
-        <v>0</v>
-      </c>
       <c r="R251" t="n">
         <v>0</v>
       </c>
@@ -48141,9 +47868,6 @@
       <c r="O254" t="n">
         <v>3</v>
       </c>
-      <c r="Q254" t="n">
-        <v>0</v>
-      </c>
       <c r="R254" t="n">
         <v>0.006342612649636899</v>
       </c>
@@ -48390,7 +48114,7 @@
       </c>
       <c r="AM255" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN255" t="b">
@@ -48537,9 +48261,6 @@
       <c r="O256" t="n">
         <v>0</v>
       </c>
-      <c r="Q256" t="n">
-        <v>0</v>
-      </c>
       <c r="R256" t="n">
         <v>0</v>
       </c>
@@ -49095,9 +48816,6 @@
       <c r="O259" t="n">
         <v>0</v>
       </c>
-      <c r="Q259" t="n">
-        <v>0</v>
-      </c>
       <c r="R259" t="n">
         <v>0</v>
       </c>
@@ -49653,9 +49371,6 @@
       <c r="O262" t="n">
         <v>5</v>
       </c>
-      <c r="Q262" t="n">
-        <v>0</v>
-      </c>
       <c r="R262" t="n">
         <v>0.01057102108272817</v>
       </c>
@@ -49902,7 +49617,7 @@
       </c>
       <c r="AM263" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN263" t="b">
@@ -50049,9 +49764,6 @@
       <c r="O264" t="n">
         <v>0</v>
       </c>
-      <c r="Q264" t="n">
-        <v>0</v>
-      </c>
       <c r="R264" t="n">
         <v>0</v>
       </c>
@@ -50607,9 +50319,6 @@
       <c r="O267" t="n">
         <v>0</v>
       </c>
-      <c r="Q267" t="n">
-        <v>0</v>
-      </c>
       <c r="R267" t="n">
         <v>0</v>
       </c>
@@ -51165,9 +50874,6 @@
       <c r="O270" t="n">
         <v>41</v>
       </c>
-      <c r="Q270" t="n">
-        <v>0</v>
-      </c>
       <c r="R270" t="n">
         <v>0.08629006504282023</v>
       </c>
@@ -51414,7 +51120,7 @@
       </c>
       <c r="AM271" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN271" t="b">
@@ -51561,9 +51267,6 @@
       <c r="O272" t="n">
         <v>0</v>
       </c>
-      <c r="Q272" t="n">
-        <v>0</v>
-      </c>
       <c r="R272" t="n">
         <v>0</v>
       </c>
@@ -52119,9 +51822,6 @@
       <c r="O275" t="n">
         <v>0</v>
       </c>
-      <c r="Q275" t="n">
-        <v>0</v>
-      </c>
       <c r="R275" t="n">
         <v>0</v>
       </c>
@@ -52677,9 +52377,6 @@
       <c r="O278" t="n">
         <v>6</v>
       </c>
-      <c r="Q278" t="n">
-        <v>0</v>
-      </c>
       <c r="R278" t="n">
         <v>0.01262781439651028</v>
       </c>
@@ -52926,7 +52623,7 @@
       </c>
       <c r="AM279" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN279" t="b">
@@ -53073,9 +52770,6 @@
       <c r="O280" t="n">
         <v>1</v>
       </c>
-      <c r="Q280" t="n">
-        <v>0</v>
-      </c>
       <c r="R280" t="n">
         <v>0.02190739350432638</v>
       </c>
@@ -53631,9 +53325,6 @@
       <c r="O283" t="n">
         <v>0</v>
       </c>
-      <c r="Q283" t="n">
-        <v>0</v>
-      </c>
       <c r="R283" t="n">
         <v>0</v>
       </c>
@@ -54189,9 +53880,6 @@
       <c r="O286" t="n">
         <v>12</v>
       </c>
-      <c r="Q286" t="n">
-        <v>0</v>
-      </c>
       <c r="R286" t="n">
         <v>0.02525562879302055</v>
       </c>
@@ -54438,7 +54126,7 @@
       </c>
       <c r="AM287" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN287" t="b">
@@ -54585,9 +54273,6 @@
       <c r="O288" t="n">
         <v>2</v>
       </c>
-      <c r="Q288" t="n">
-        <v>0</v>
-      </c>
       <c r="R288" t="n">
         <v>0.04381478700865277</v>
       </c>
@@ -55291,9 +54976,6 @@
       <c r="O292" t="n">
         <v>0</v>
       </c>
-      <c r="Q292" t="n">
-        <v>0</v>
-      </c>
       <c r="R292" t="n">
         <v>0</v>
       </c>
@@ -55849,9 +55531,6 @@
       <c r="O295" t="n">
         <v>2</v>
       </c>
-      <c r="Q295" t="n">
-        <v>0</v>
-      </c>
       <c r="R295" t="n">
         <v>0.004209271465503426</v>
       </c>
@@ -56098,7 +55777,7 @@
       </c>
       <c r="AM296" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN296" t="b">
@@ -56245,9 +55924,6 @@
       <c r="O297" t="n">
         <v>1</v>
       </c>
-      <c r="Q297" t="n">
-        <v>0</v>
-      </c>
       <c r="R297" t="n">
         <v>0.02190739350432638</v>
       </c>
@@ -56951,9 +56627,6 @@
       <c r="O301" t="n">
         <v>3</v>
       </c>
-      <c r="Q301" t="n">
-        <v>0</v>
-      </c>
       <c r="R301" t="n">
         <v>0.05754893337847727</v>
       </c>
@@ -57509,9 +57182,6 @@
       <c r="O304" t="n">
         <v>0</v>
       </c>
-      <c r="Q304" t="n">
-        <v>0</v>
-      </c>
       <c r="R304" t="n">
         <v>0</v>
       </c>
@@ -57758,7 +57428,7 @@
       </c>
       <c r="AM305" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN305" t="b">
@@ -57905,9 +57575,6 @@
       <c r="O306" t="n">
         <v>4</v>
       </c>
-      <c r="Q306" t="n">
-        <v>0</v>
-      </c>
       <c r="R306" t="n">
         <v>0.08762957401730553</v>
       </c>
@@ -58611,9 +58278,6 @@
       <c r="O310" t="n">
         <v>0</v>
       </c>
-      <c r="Q310" t="n">
-        <v>0</v>
-      </c>
       <c r="R310" t="n">
         <v>0</v>
       </c>
@@ -59169,9 +58833,6 @@
       <c r="O313" t="n">
         <v>2</v>
       </c>
-      <c r="Q313" t="n">
-        <v>0</v>
-      </c>
       <c r="R313" t="n">
         <v>0.004209271465503426</v>
       </c>
@@ -59418,7 +59079,7 @@
       </c>
       <c r="AM314" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN314" t="b">
@@ -59565,9 +59226,6 @@
       <c r="O315" t="n">
         <v>2</v>
       </c>
-      <c r="Q315" t="n">
-        <v>0</v>
-      </c>
       <c r="R315" t="n">
         <v>0.04381478700865277</v>
       </c>
@@ -60123,9 +59781,6 @@
       <c r="O318" t="n">
         <v>0</v>
       </c>
-      <c r="Q318" t="n">
-        <v>0</v>
-      </c>
       <c r="R318" t="n">
         <v>0</v>
       </c>
@@ -60681,9 +60336,6 @@
       <c r="O321" t="n">
         <v>3</v>
       </c>
-      <c r="Q321" t="n">
-        <v>0</v>
-      </c>
       <c r="R321" t="n">
         <v>0.006313907198255139</v>
       </c>
@@ -60930,7 +60582,7 @@
       </c>
       <c r="AM322" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN322" t="b">
@@ -61077,9 +60729,6 @@
       <c r="O323" t="n">
         <v>0</v>
       </c>
-      <c r="Q323" t="n">
-        <v>0</v>
-      </c>
       <c r="R323" t="n">
         <v>0</v>
       </c>
@@ -61635,9 +61284,6 @@
       <c r="O326" t="n">
         <v>0</v>
       </c>
-      <c r="Q326" t="n">
-        <v>0</v>
-      </c>
       <c r="R326" t="n">
         <v>0</v>
       </c>
@@ -62193,9 +61839,6 @@
       <c r="O329" t="n">
         <v>5</v>
       </c>
-      <c r="Q329" t="n">
-        <v>0</v>
-      </c>
       <c r="R329" t="n">
         <v>0.01052317866375857</v>
       </c>
@@ -62442,7 +62085,7 @@
       </c>
       <c r="AM330" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN330" t="b">
@@ -62589,9 +62232,6 @@
       <c r="O331" t="n">
         <v>2</v>
       </c>
-      <c r="Q331" t="n">
-        <v>0</v>
-      </c>
       <c r="R331" t="n">
         <v>0.04381478700865277</v>
       </c>
@@ -63295,9 +62935,6 @@
       <c r="O335" t="n">
         <v>0</v>
       </c>
-      <c r="Q335" t="n">
-        <v>0</v>
-      </c>
       <c r="R335" t="n">
         <v>0</v>
       </c>
@@ -63853,9 +63490,6 @@
       <c r="O338" t="n">
         <v>7</v>
       </c>
-      <c r="Q338" t="n">
-        <v>0</v>
-      </c>
       <c r="R338" t="n">
         <v>0.01473245012926199</v>
       </c>
@@ -64102,7 +63736,7 @@
       </c>
       <c r="AM339" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN339" t="b">
@@ -64249,9 +63883,6 @@
       <c r="O340" t="n">
         <v>2</v>
       </c>
-      <c r="Q340" t="n">
-        <v>0</v>
-      </c>
       <c r="R340" t="n">
         <v>0.04381478700865277</v>
       </c>
@@ -64955,9 +64586,6 @@
       <c r="O344" t="n">
         <v>1</v>
       </c>
-      <c r="Q344" t="n">
-        <v>0</v>
-      </c>
       <c r="R344" t="n">
         <v>0.01918297779282576</v>
       </c>
@@ -65513,9 +65141,6 @@
       <c r="O347" t="n">
         <v>5</v>
       </c>
-      <c r="Q347" t="n">
-        <v>0</v>
-      </c>
       <c r="R347" t="n">
         <v>0.01052317866375857</v>
       </c>
@@ -65762,7 +65387,7 @@
       </c>
       <c r="AM348" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN348" t="b">
@@ -65909,9 +65534,6 @@
       <c r="O349" t="n">
         <v>0</v>
       </c>
-      <c r="Q349" t="n">
-        <v>0</v>
-      </c>
       <c r="R349" t="n">
         <v>0</v>
       </c>
@@ -66615,9 +66237,6 @@
       <c r="O353" t="n">
         <v>0</v>
       </c>
-      <c r="Q353" t="n">
-        <v>0</v>
-      </c>
       <c r="R353" t="n">
         <v>0</v>
       </c>
@@ -67173,9 +66792,6 @@
       <c r="O356" t="n">
         <v>3</v>
       </c>
-      <c r="Q356" t="n">
-        <v>0</v>
-      </c>
       <c r="R356" t="n">
         <v>0.006313907198255139</v>
       </c>
@@ -67422,7 +67038,7 @@
       </c>
       <c r="AM357" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN357" t="b">
@@ -67569,9 +67185,6 @@
       <c r="O358" t="n">
         <v>1</v>
       </c>
-      <c r="Q358" t="n">
-        <v>0</v>
-      </c>
       <c r="R358" t="n">
         <v>0.02190739350432638</v>
       </c>
@@ -68275,9 +67888,6 @@
       <c r="O362" t="n">
         <v>0</v>
       </c>
-      <c r="Q362" t="n">
-        <v>0</v>
-      </c>
       <c r="R362" t="n">
         <v>0</v>
       </c>
@@ -68833,9 +68443,6 @@
       <c r="O365" t="n">
         <v>2</v>
       </c>
-      <c r="Q365" t="n">
-        <v>0</v>
-      </c>
       <c r="R365" t="n">
         <v>0.004209271465503426</v>
       </c>
@@ -69082,7 +68689,7 @@
       </c>
       <c r="AM366" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN366" t="b">
@@ -69229,9 +68836,6 @@
       <c r="O367" t="n">
         <v>0</v>
       </c>
-      <c r="Q367" t="n">
-        <v>0</v>
-      </c>
       <c r="R367" t="n">
         <v>0</v>
       </c>
@@ -69935,9 +69539,6 @@
       <c r="O371" t="n">
         <v>0</v>
       </c>
-      <c r="Q371" t="n">
-        <v>0</v>
-      </c>
       <c r="R371" t="n">
         <v>0</v>
       </c>
@@ -70493,9 +70094,6 @@
       <c r="O374" t="n">
         <v>6</v>
       </c>
-      <c r="Q374" t="n">
-        <v>0</v>
-      </c>
       <c r="R374" t="n">
         <v>0.01257938759788323</v>
       </c>
@@ -70742,7 +70340,7 @@
       </c>
       <c r="AM375" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN375" t="b">
@@ -70889,9 +70487,6 @@
       <c r="O376" t="n">
         <v>0</v>
       </c>
-      <c r="Q376" t="n">
-        <v>0</v>
-      </c>
       <c r="R376" t="n">
         <v>0</v>
       </c>
@@ -71447,9 +71042,6 @@
       <c r="O379" t="n">
         <v>1</v>
       </c>
-      <c r="Q379" t="n">
-        <v>0</v>
-      </c>
       <c r="R379" t="n">
         <v>0.01912723205234435</v>
       </c>
@@ -72005,9 +71597,6 @@
       <c r="O382" t="n">
         <v>1</v>
       </c>
-      <c r="Q382" t="n">
-        <v>0</v>
-      </c>
       <c r="R382" t="n">
         <v>0.002096564599647205</v>
       </c>
@@ -72254,7 +71843,7 @@
       </c>
       <c r="AM383" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN383" t="b">
@@ -72401,9 +71990,6 @@
       <c r="O384" t="n">
         <v>0</v>
       </c>
-      <c r="Q384" t="n">
-        <v>0</v>
-      </c>
       <c r="R384" t="n">
         <v>0</v>
       </c>
@@ -72959,9 +72545,6 @@
       <c r="O387" t="n">
         <v>2</v>
       </c>
-      <c r="Q387" t="n">
-        <v>0</v>
-      </c>
       <c r="R387" t="n">
         <v>0.0382544641046887</v>
       </c>
@@ -73517,9 +73100,6 @@
       <c r="O390" t="n">
         <v>6</v>
       </c>
-      <c r="Q390" t="n">
-        <v>0</v>
-      </c>
       <c r="R390" t="n">
         <v>0.01257938759788323</v>
       </c>
@@ -73766,7 +73346,7 @@
       </c>
       <c r="AM391" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN391" t="b">
@@ -73913,9 +73493,6 @@
       <c r="O392" t="n">
         <v>2</v>
       </c>
-      <c r="Q392" t="n">
-        <v>0</v>
-      </c>
       <c r="R392" t="n">
         <v>0.04355644943068999</v>
       </c>
@@ -74471,9 +74048,6 @@
       <c r="O395" t="n">
         <v>1</v>
       </c>
-      <c r="Q395" t="n">
-        <v>0</v>
-      </c>
       <c r="R395" t="n">
         <v>0.01912723205234435</v>
       </c>
@@ -75029,9 +74603,6 @@
       <c r="O398" t="n">
         <v>1</v>
       </c>
-      <c r="Q398" t="n">
-        <v>0</v>
-      </c>
       <c r="R398" t="n">
         <v>0.002096564599647205</v>
       </c>
@@ -75278,7 +74849,7 @@
       </c>
       <c r="AM399" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN399" t="b">
@@ -75425,9 +74996,6 @@
       <c r="O400" t="n">
         <v>0</v>
       </c>
-      <c r="Q400" t="n">
-        <v>0</v>
-      </c>
       <c r="R400" t="n">
         <v>0</v>
       </c>
@@ -76131,9 +75699,6 @@
       <c r="O404" t="n">
         <v>2</v>
       </c>
-      <c r="Q404" t="n">
-        <v>0</v>
-      </c>
       <c r="R404" t="n">
         <v>0.0382544641046887</v>
       </c>
@@ -76689,9 +76254,6 @@
       <c r="O407" t="n">
         <v>3</v>
       </c>
-      <c r="Q407" t="n">
-        <v>0</v>
-      </c>
       <c r="R407" t="n">
         <v>0.006289693798941615</v>
       </c>
@@ -76938,7 +76500,7 @@
       </c>
       <c r="AM408" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN408" t="b">
@@ -77085,9 +76647,6 @@
       <c r="O409" t="n">
         <v>1</v>
       </c>
-      <c r="Q409" t="n">
-        <v>0</v>
-      </c>
       <c r="R409" t="n">
         <v>0.02177822471534499</v>
       </c>
@@ -77791,9 +77350,6 @@
       <c r="O413" t="n">
         <v>1</v>
       </c>
-      <c r="Q413" t="n">
-        <v>0</v>
-      </c>
       <c r="R413" t="n">
         <v>0.01912723205234435</v>
       </c>
@@ -78349,9 +77905,6 @@
       <c r="O416" t="n">
         <v>1</v>
       </c>
-      <c r="Q416" t="n">
-        <v>0</v>
-      </c>
       <c r="R416" t="n">
         <v>0.002096564599647205</v>
       </c>
@@ -78598,7 +78151,7 @@
       </c>
       <c r="AM417" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN417" t="b">
@@ -78745,9 +78298,6 @@
       <c r="O418" t="n">
         <v>3</v>
       </c>
-      <c r="Q418" t="n">
-        <v>0</v>
-      </c>
       <c r="R418" t="n">
         <v>0.06533467414603497</v>
       </c>
@@ -79451,9 +79001,6 @@
       <c r="O422" t="n">
         <v>1</v>
       </c>
-      <c r="Q422" t="n">
-        <v>0</v>
-      </c>
       <c r="R422" t="n">
         <v>0.01912723205234435</v>
       </c>
@@ -80009,9 +79556,6 @@
       <c r="O425" t="n">
         <v>4</v>
       </c>
-      <c r="Q425" t="n">
-        <v>0</v>
-      </c>
       <c r="R425" t="n">
         <v>0.008386258398588819</v>
       </c>
@@ -80258,7 +79802,7 @@
       </c>
       <c r="AM426" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN426" t="b">
@@ -80405,9 +79949,6 @@
       <c r="O427" t="n">
         <v>6</v>
       </c>
-      <c r="Q427" t="n">
-        <v>0</v>
-      </c>
       <c r="R427" t="n">
         <v>0.1306693482920699</v>
       </c>
@@ -81111,9 +80652,6 @@
       <c r="O431" t="n">
         <v>1</v>
       </c>
-      <c r="Q431" t="n">
-        <v>0</v>
-      </c>
       <c r="R431" t="n">
         <v>0.01912723205234435</v>
       </c>
@@ -81669,9 +81207,6 @@
       <c r="O434" t="n">
         <v>5</v>
       </c>
-      <c r="Q434" t="n">
-        <v>0</v>
-      </c>
       <c r="R434" t="n">
         <v>0.01048282299823602</v>
       </c>
@@ -81918,7 +81453,7 @@
       </c>
       <c r="AM435" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN435" t="b">
@@ -82065,9 +81600,6 @@
       <c r="O436" t="n">
         <v>6</v>
       </c>
-      <c r="Q436" t="n">
-        <v>0</v>
-      </c>
       <c r="R436" t="n">
         <v>0.1306693482920699</v>
       </c>
@@ -82771,9 +82303,6 @@
       <c r="O440" t="n">
         <v>0</v>
       </c>
-      <c r="Q440" t="n">
-        <v>0</v>
-      </c>
       <c r="R440" t="n">
         <v>0</v>
       </c>
@@ -83329,9 +82858,6 @@
       <c r="O443" t="n">
         <v>5</v>
       </c>
-      <c r="Q443" t="n">
-        <v>0</v>
-      </c>
       <c r="R443" t="n">
         <v>0.01048282299823602</v>
       </c>
@@ -83578,7 +83104,7 @@
       </c>
       <c r="AM444" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN444" t="b">
@@ -83725,9 +83251,6 @@
       <c r="O445" t="n">
         <v>0</v>
       </c>
-      <c r="Q445" t="n">
-        <v>0</v>
-      </c>
       <c r="R445" t="n">
         <v>0</v>
       </c>
@@ -84431,9 +83954,6 @@
       <c r="O449" t="n">
         <v>0</v>
       </c>
-      <c r="Q449" t="n">
-        <v>0</v>
-      </c>
       <c r="R449" t="n">
         <v>0</v>
       </c>
@@ -84989,9 +84509,6 @@
       <c r="O452" t="n">
         <v>5</v>
       </c>
-      <c r="Q452" t="n">
-        <v>0</v>
-      </c>
       <c r="R452" t="n">
         <v>0.01048282299823602</v>
       </c>
@@ -85238,7 +84755,7 @@
       </c>
       <c r="AM453" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN453" t="b">
@@ -85385,9 +84902,6 @@
       <c r="O454" t="n">
         <v>1</v>
       </c>
-      <c r="Q454" t="n">
-        <v>0</v>
-      </c>
       <c r="R454" t="n">
         <v>0.02177822471534499</v>
       </c>
@@ -86091,9 +85605,6 @@
       <c r="O458" t="n">
         <v>0</v>
       </c>
-      <c r="Q458" t="n">
-        <v>0</v>
-      </c>
       <c r="R458" t="n">
         <v>0</v>
       </c>
@@ -86649,9 +86160,6 @@
       <c r="O461" t="n">
         <v>5</v>
       </c>
-      <c r="Q461" t="n">
-        <v>0</v>
-      </c>
       <c r="R461" t="n">
         <v>0.01048282299823602</v>
       </c>
@@ -86898,7 +86406,7 @@
       </c>
       <c r="AM462" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN462" t="b">
@@ -87045,9 +86553,6 @@
       <c r="O463" t="n">
         <v>3</v>
       </c>
-      <c r="Q463" t="n">
-        <v>0</v>
-      </c>
       <c r="R463" t="n">
         <v>0.06533467414603497</v>
       </c>
@@ -87751,9 +87256,6 @@
       <c r="O467" t="n">
         <v>0</v>
       </c>
-      <c r="Q467" t="n">
-        <v>0</v>
-      </c>
       <c r="R467" t="n">
         <v>0</v>
       </c>
@@ -88309,9 +87811,6 @@
       <c r="O470" t="n">
         <v>3</v>
       </c>
-      <c r="Q470" t="n">
-        <v>0</v>
-      </c>
       <c r="R470" t="n">
         <v>0.006289693798941615</v>
       </c>
@@ -88558,7 +88057,7 @@
       </c>
       <c r="AM471" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN471" t="b">
@@ -88704,9 +88203,6 @@
       </c>
       <c r="O472" t="n">
         <v>1</v>
-      </c>
-      <c r="Q472" t="n">
-        <v>0</v>
       </c>
       <c r="R472" t="n">
         <v>0.02177822471534499</v>
